--- a/#Japan_anonymized.xlsx
+++ b/#Japan_anonymized.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -6067,7 +6067,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -7025,7 +7025,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
@@ -10222,7 +10222,7 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
@@ -10988,7 +10988,7 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K264" t="inlineStr"/>
@@ -11311,7 +11311,7 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K271" t="inlineStr"/>
@@ -11992,7 +11992,7 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K289" t="inlineStr"/>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K310" t="inlineStr"/>
@@ -13038,7 +13038,7 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K317" t="inlineStr"/>
@@ -13943,7 +13943,7 @@
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K338" t="inlineStr"/>
@@ -14662,7 +14662,7 @@
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K357" t="inlineStr"/>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K377" t="inlineStr"/>
@@ -16280,7 +16280,7 @@
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K398" t="inlineStr"/>
@@ -16328,7 +16328,7 @@
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K399" t="inlineStr"/>
@@ -17125,7 +17125,7 @@
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K420" t="inlineStr"/>
@@ -17968,7 +17968,7 @@
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K441" t="inlineStr"/>
@@ -18415,7 +18415,7 @@
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K453" t="inlineStr"/>
@@ -19082,7 +19082,7 @@
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K471" t="inlineStr"/>
@@ -19908,7 +19908,7 @@
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K493" t="inlineStr"/>
@@ -20677,7 +20677,7 @@
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K514" t="inlineStr"/>
@@ -21434,7 +21434,7 @@
       </c>
       <c r="J534" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K534" t="inlineStr"/>
@@ -22194,7 +22194,7 @@
       </c>
       <c r="J554" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K554" t="inlineStr"/>
@@ -22238,7 +22238,7 @@
       </c>
       <c r="J555" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K555" t="inlineStr"/>
@@ -23155,7 +23155,7 @@
       </c>
       <c r="J577" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K577" t="inlineStr"/>
@@ -23198,7 +23198,7 @@
       </c>
       <c r="J578" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K578" t="inlineStr"/>
@@ -23244,7 +23244,7 @@
       </c>
       <c r="J579" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K579" t="inlineStr"/>
@@ -24089,7 +24089,7 @@
       </c>
       <c r="J600" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K600" t="inlineStr"/>
@@ -24813,7 +24813,7 @@
       </c>
       <c r="J619" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K619" t="inlineStr"/>
@@ -25585,7 +25585,7 @@
       </c>
       <c r="J640" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K640" t="inlineStr"/>
@@ -26353,7 +26353,7 @@
       </c>
       <c r="J661" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K661" t="inlineStr"/>
@@ -27169,7 +27169,7 @@
       </c>
       <c r="J681" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K681" t="inlineStr"/>
@@ -27221,7 +27221,7 @@
       </c>
       <c r="J682" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K682" t="inlineStr"/>
@@ -28005,7 +28005,7 @@
       </c>
       <c r="J703" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K703" t="inlineStr"/>
@@ -28824,7 +28824,7 @@
       </c>
       <c r="J724" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K724" t="inlineStr"/>
@@ -29611,7 +29611,7 @@
       </c>
       <c r="J745" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K745" t="inlineStr"/>
@@ -30331,7 +30331,7 @@
       </c>
       <c r="J764" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K764" t="inlineStr"/>
@@ -31116,7 +31116,7 @@
       </c>
       <c r="J783" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K783" t="inlineStr"/>
@@ -31969,7 +31969,7 @@
       </c>
       <c r="J805" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K805" t="inlineStr"/>
@@ -32753,7 +32753,7 @@
       </c>
       <c r="J826" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K826" t="inlineStr"/>
@@ -33534,7 +33534,7 @@
       </c>
       <c r="J847" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K847" t="inlineStr"/>
@@ -34334,7 +34334,7 @@
       </c>
       <c r="J868" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K868" t="inlineStr"/>
@@ -34379,7 +34379,7 @@
       </c>
       <c r="J869" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K869" t="inlineStr"/>
@@ -34604,7 +34604,7 @@
       </c>
       <c r="J875" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K875" t="inlineStr"/>
@@ -35364,7 +35364,7 @@
       </c>
       <c r="J894" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K894" t="inlineStr"/>
@@ -35408,7 +35408,7 @@
       </c>
       <c r="J895" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K895" t="inlineStr"/>
@@ -36201,7 +36201,7 @@
       </c>
       <c r="J914" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K914" t="inlineStr"/>
@@ -37174,7 +37174,7 @@
       </c>
       <c r="J936" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K936" t="inlineStr"/>
